--- a/Assets/StreamingAssets/HGF/FirstScript.xlsx
+++ b/Assets/StreamingAssets/HGF/FirstScript.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -11,6 +11,7 @@
     <sheet name="剧情脚本" sheetId="2" r:id="rId2"/>
     <sheet name="S1" sheetId="3" r:id="rId3"/>
     <sheet name="S2" sheetId="4" r:id="rId4"/>
+    <sheet name="S3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>标题</t>
   </si>
@@ -38,10 +39,10 @@
     <t>简介</t>
   </si>
   <si>
-    <t>引导章节</t>
-  </si>
-  <si>
-    <t>这个章节用于选择观看演示故事还是观看使用教程</t>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>展示当前版本和之前版本的介绍以及演示</t>
   </si>
   <si>
     <t>类型</t>
@@ -65,16 +66,16 @@
     <t>AddCharacter</t>
   </si>
   <si>
-    <t>me</t>
-  </si>
-  <si>
-    <t>ToShow</t>
+    <t>空</t>
+  </si>
+  <si>
+    <t>Outside-ToLeft</t>
   </si>
   <si>
     <t>Speak</t>
   </si>
   <si>
-    <t>请问你要看哪个？</t>
+    <t>请问你要访问什么内容？</t>
   </si>
   <si>
     <t>TexDraw</t>
@@ -86,28 +87,46 @@
     <t>S1</t>
   </si>
   <si>
-    <t>观看演示故事</t>
+    <t>永远不变的预计完成时间</t>
+  </si>
+  <si>
+    <t>TMP</t>
   </si>
   <si>
     <t>S2</t>
   </si>
   <si>
-    <t>观看使用说明</t>
-  </si>
-  <si>
-    <t>再次点击将跳转演示故事。</t>
+    <t>V1.1更新说明</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>往期内容</t>
+  </si>
+  <si>
+    <t>占位</t>
+  </si>
+  <si>
+    <t>你选择了观看演示：永远不变的预计完成时间。</t>
   </si>
   <si>
     <t>NextScript</t>
   </si>
   <si>
-    <t>ExampleStory</t>
-  </si>
-  <si>
-    <t>再次点击将跳转使用介绍。</t>
-  </si>
-  <si>
-    <t>UsingGuide</t>
+    <t>PresentationV1.1</t>
+  </si>
+  <si>
+    <t>你选择了V1.1更新说明。</t>
+  </si>
+  <si>
+    <t>UsingGuideV1.1</t>
+  </si>
+  <si>
+    <t>你选择了访问往期内容。</t>
+  </si>
+  <si>
+    <t>PreviousContent</t>
   </si>
 </sst>
 </file>
@@ -728,7 +747,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -792,6 +811,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1048,18 +1074,18 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="84" spans="1:2">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="70" spans="1:2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1073,15 +1099,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="26.4545454545455" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="16.5818181818182" customWidth="1"/>
+    <col min="2" max="2" width="19.4272727272727" customWidth="1"/>
+    <col min="3" max="3" width="23.4636363636364" customWidth="1"/>
+    <col min="4" max="4" width="20.8545454545455" customWidth="1"/>
+    <col min="5" max="5" width="18.8" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1100,171 +1129,90 @@
       <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="28" spans="1:7">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:4">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:5">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1">
-        <v>1111</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1279,8 +1227,8 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.4181818181818" customWidth="1"/>
-    <col min="3" max="3" width="17.6818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.2818181818182" customWidth="1"/>
+    <col min="3" max="3" width="34.6545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1303,28 +1251,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="28" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1339,8 +1292,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.6636363636364" customWidth="1"/>
-    <col min="3" max="3" width="11.9272727272727" customWidth="1"/>
+    <col min="1" max="1" width="11.1363636363636" customWidth="1"/>
+    <col min="2" max="2" width="13.6909090909091" customWidth="1"/>
+    <col min="3" max="3" width="24.8272727272727" customWidth="1"/>
+    <col min="4" max="4" width="10.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="11.6454545454545" customWidth="1"/>
+    <col min="6" max="6" width="9.99090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1363,27 +1320,84 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.0181818181818" customWidth="1"/>
+    <col min="3" max="3" width="24.2727272727273" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
